--- a/Re-Imagination/testdata/LC_TestScenarios.xlsx
+++ b/Re-Imagination/testdata/LC_TestScenarios.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="106">
   <si>
     <t>Product Type</t>
   </si>
@@ -346,6 +346,12 @@
   </si>
   <si>
     <t>4086165</t>
+  </si>
+  <si>
+    <t>4087856</t>
+  </si>
+  <si>
+    <t>4087857</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1167,7 @@
         <v>307</v>
       </c>
       <c r="H12" t="s" s="3">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I12" s="5"/>
     </row>
@@ -2404,7 +2410,7 @@
       </c>
       <c r="G63" s="8"/>
       <c r="H63" t="s" s="3">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I63" s="8"/>
     </row>
